--- a/data/daily/2026-09/2026-09-14.xlsx
+++ b/data/daily/2026-09/2026-09-14.xlsx
@@ -357,17 +357,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -388,11 +413,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -413,11 +438,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -438,11 +463,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -463,11 +488,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -488,11 +513,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -513,11 +538,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -538,11 +563,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -563,11 +588,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -588,11 +613,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -613,11 +638,11 @@
     <ext cx="457200" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -835,6 +860,31 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
@@ -843,11 +893,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -868,11 +918,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -893,11 +943,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -918,11 +968,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -943,11 +993,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -968,11 +1018,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -993,11 +1043,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1018,11 +1068,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1043,11 +1093,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1068,11 +1118,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1093,11 +1143,11 @@
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1120,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1142,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1167,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1375,27 +1425,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1403,24 +1478,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1428,74 +1503,124 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,104 +1628,29 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2550,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 및 활력 충전 — 섭취 후 피로감이 줄고 신체에 빠른 활력이 생김</t>
+          <t>뛰어난 피로 회복 효과 — 힘이 없을 때 섭취 시 활력이 생기고 피로 해소에 큰 도움이 됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>뛰어난 체감 효과 — 몸에 잘 받고 힘이 없는 날 먹으면 효과를 체감함</t>
+          <t>맛있는 맛과 간편함 — 맛이 좋고 부담 없이 간편하게 먹기 용이함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 받았을 때 기분이 좋고 부담 없이 선물하기 적합함</t>
+          <t>알찬 추가 증정 구성 — 덤으로 하나 더 증정되어 선물용 및 복용 시 만족감이 높음</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2609,18 +2659,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>개운한 컨디션 회복 — 면역력이 떨어지거나 바쁜 날 섭취 시 개운함과 활력을 느낌</t>
+          <t>확실한 피로 회복 및 활력 — 섭취 후 피로감이 줄어들고 다음 날 몸이 훨씬 개운해짐</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>상큼하고 달콤한 맛 — 텁텁함 없이 상큼하고 달달한 복숭아 맛으로 부담 없이 먹음</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>상큼달콤한 복숭아 맛 — 신맛이나 텁텁함이 적고 상큼달콤하여 가볍게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>알찬 10+1 증정 혜택 — 10개 구매 시 1개를 추가 증정하여 알차게 구성됨</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 관련 미수령 문제 — 배송 기사 연락 문제 등으로 상품을 받지 못하는 불편 발생</t>
+          <t>상품 배송 미수령 문제 — 구매 결정은 되었으나 실제 상품을 수령하지 못함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2664,23 +2718,19 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>지속적인 피로 해소 — 꾸준히 먹으면 지속되던 피로가 풀리고 힘이 남</t>
+          <t>지속된 피로 해소 — 복용 시 피로가 잘 풀리고 몸에 에너지가 생김</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 고급스럽게 도착하여 선물용 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>부담 없는 뛰어난 맛 — 맛있게 먹을 수 있는 비타민으로 복용 부담이 없음</t>
-        </is>
-      </c>
+          <t>맛있는 맛과 고급 포장 — 맛이 좋고 포장이 고급스러워 선물용으로 제격임</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2723,21 +2773,21 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8701</v>
+        <v>8702</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>간편한 올인원 비타민 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함</t>
+          <t>빠른 컨디션 회복 — 독감 회복기나 피로할 때 생기 회복에 도움이 됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 단독 구성으로 추가 2입이 더 들어있어 알차게 느껴짐</t>
+          <t>간편한 올인원 섭취 — 여러 영양제를 챙길 필요 없이 한 번에 간편 섭취 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>기력 회복 보조 효과 — 피로감이 덜하고 힘들 때 체력을 회복하는 느낌을 받음</t>
+          <t>단독 구성 추가 증정 — 7입에 2입을 추가 증정하여 구성이 알참</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2786,25 +2836,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>섭취가 편한 구미 제형 — 알약 거부감 없이 과일 향 젤리처럼 즐겁게 챙겨 먹음</t>
+          <t>맛있고 쫀득한 구미 제형 — 새콤달콤한 과일 향 젤리 제형으로 거부감 없이 즐겨 먹음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>꼼꼼한 포장과 배송 — 배송이 빠르고 포장 상태가 매우 꼼꼼함</t>
+          <t>간편한 일상 영양 보충 — 알약 형태가 아니라 물 없이 간식처럼 쉽게 챙겨 먹음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>효과 체감의 불명확함 — 맛있게 먹을 수 있으나 효능에 대한 직접적 체감은 부족함</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>미세한 씁쓸한 뒷맛 — 달지 않고 약간의 씁쓸한 맛이 느껴지기도 함</t>
-        </is>
-      </c>
+          <t>약간의 씁쓸한 맛 감돎 — 달콤함 외에 미세하게 씁쓸한 잔맛이 남음</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -2845,21 +2891,21 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 피곤한 일상에서 하나만 챙겨 먹어도 컨디션이 회복됨</t>
+          <t>목넘김이 쉬운 알약 크기 — 알약 크기가 크지 않아 목넘김이 용이함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>예쁜 선물 포장 패키지 — 선물용 포장이 이쁘게 되어 있어 주고받기에 감동적임</t>
+          <t>빠른 컨디션 회복 — 피로가 누적되었을 때 먹으면 컨디션 회복에 효과적임</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>간편한 섭취 방식 — 멀티비타민 형태라 귀찮지 않고 마시기 편함</t>
+          <t>선물용으로 우수한 패키지 — 예쁘게 선물 포장되어 있어 부담 없이 전달하기 좋음</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2908,20 +2954,16 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효능 — 피곤하고 컨디션이 안 좋을 때 회복 효과를 크게 체감함</t>
+          <t>확실한 컨디션 회복 — 피로감이 심할 때 복용하면 빠른 회복에 도움 됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>우수한 휴대성 및 편의성 — 가지고 다니기 편하고 마시기 간편함</t>
+          <t>우수한 휴대성 및 편의성 — 마시기 편하고 가지고 다니기 적합함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>높은 가격 부담 — 제품 성능은 좋으나 가격대가 비싼 편임</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -2963,23 +3005,19 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 원스톱 섭취 — 눌러서 분말과 액상을 섞어 바로 마시는 형태라 편리함</t>
+          <t>부담 없는 복용감 — 홍삼 특유의 쓴맛이 적고 액상과 분말을 한 번에 먹기 편함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 깔끔한 맛 — 홍삼 성분임에도 쓴맛이 부담스럽지 않고 깔끔함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>깔끔한 패키지와 혜택 — 포장이 깔끔하며 1입 추가 증정 구성이 알참</t>
-        </is>
-      </c>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드로 믿음이 가며 추가 증정 구성도 알참</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -3026,19 +3064,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>피로감 완화 및 개운함 — 힘들 때 마시면 다음 날 피로감이 덜하고 개운함</t>
+          <t>개운한 피로 개선 — 마신 후 피로감이 덜하고 개운함이 체감됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 포장이 고급스러워 선물용으로 받는 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>맛있는 액상 비타민 — 일반 알약과 다르고 맛이 있어 섭취하기 좋음</t>
-        </is>
-      </c>
+          <t>고급스러운 포장 디자인 — 패키지가 고급스러워 선물용으로 기분 좋게 주고받음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3085,18 +3119,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>오래 유지되는 활력 효과 — 꾸준히 섭취 시 피로함이 덜하고 반짝이는 기분이 오래 유지됨</t>
+          <t>지속되는 피로 완화 — 꾸준히 먹으면 피로가 덜하고 활력이 오래 유지됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>깔끔한 포장 및 휴대성 — 포장이 깔끔하여 선물 느낌이 나고 들고 다니며 먹기 편함</t>
+          <t>뛰어난 휴대성과 깔끔함 — 하루 하나씩 챙겨 다니기 편하고 포장이 깔끔함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>목넘김이 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>다소 큰 알약 크기 — 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3144,18 +3178,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 풍미 — 달지 않고 그냥 먹거나 물에 타 먹기 맛있는 효소임</t>
+          <t>맛있는 맛과 쉬운 섭취 — 달지 않고 맛있어 포 채 먹거나 물에 타기 편함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>만족스러운 포장 및 구성 — 포장이 예쁘고 굿즈 혜택 구성이 마음에 듦</t>
+          <t>푸짐한 구성 및 사은품 — 포토카드 등 사은품 혜택이 좋아 만족도가 높음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>탄산수 혼합 시 거품 넘침 — 탄산수에 부어 섞을 경우 거품이 일어나 넘칠 수 있음</t>
+          <t>탄산수 혼합 시 거품 — 탄산수에 부으면 거품이 일어나 넘칠 수 있음</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3164,7 +3198,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3172,58 +3206,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린 캡슐레이션 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907091018_68a44d5ed50249e7aa6ad05f30d0e480.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260914085959_597d4eafce2b4897917a1803a9f6d0ea.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>732</v>
+        <v>1654</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>고급스러운 핑크 포장 — 핑크빛 고급스러운 포장으로 선물받을 때 기분이 좋아짐</t>
+          <t>식후 더부룩함 완화 — 식사 후 섭취 시 속이 편안해지고 소화와 배변에 도움 됨</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>피부 개선 느낌 — 꾸준히 먹으면 피부가 맑아지는 듯한 체감을 줌</t>
+          <t>고소한 군고구마 맛 — 군고구마 맛으로 고소해서 매일 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>초기 효과 체감 미흡 — 섭취한 지 며칠 되지 않았을 때는 효과를 바로 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3231,62 +3261,54 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907091018_68a44d5ed50249e7aa6ad05f30d0e480.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>859</v>
+        <v>733</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>높은 가성비와 추가 증정 — 저렴한 가격에 보너스 포 및 씬칩 사은품이 추가됨</t>
+          <t>예쁘고 고급스러운 포장 — 패키지와 디자인이 매우 예뻐 선물받을 때 만족감이 높음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 포장 — 맛이 고소하여 먹기 편하고 포장이 고급스러움</t>
+          <t>피부 상태 개선 느낌 — 꾸준히 복용 시 피부가 맑아지고 탱탱해지는 기분이 듦</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>복용 초기 장 반응 발생 — 복용 직후 뱃속이 꾸르륵거리거나 가스가 차는 현상이 있음</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>배송 미수령 발생 — 일부 배송 누락으로 제품을 받지 못하는 경우 발생</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3294,51 +3316,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>213</v>
+        <v>859</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔한 맛 — 단백질 특유의 비리고 텁텁한 맛 없이 달콤하고 담백함</t>
+          <t>합리적인 가격과 증정 — 특가 판매 및 추가 증정 혜택으로 저렴하게 구매함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>편안한 속과 적당한 포만감 — 마신 후 더부룩하지 않고 식사 사이 허기를 달래기 좋음</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>슬림한 휴대용 패키지 — 슬림하여 가방에 넣고 다니며 운동 후 간편하게 마심</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>무난한 맛과 쉬운 복용 — 맛이 나쁘지 않고 복용 분량이 적당함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>선물 미배송 문제 — 선물이 정상적으로 배송되지 않음</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -3380,22 +3402,22 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 많은 수량을 매우 저렴한 가격으로 가성비 있게 구매함</t>
+          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 덜하고 부드러우며 맛이 다양해 질리지 않음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>물리지 않는 다양한 맛 — 뻑뻑함이 적고 맛이 다양하여 매일 먹어도 질리지 않음</t>
+          <t>높은 가성비 및 간편 조리 — 가격 대비 양이 많고 전자레인지로 간편 조리가 가능함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 녹아서 도착 — 배송 포장 보온 상태에 따라 제품이 녹아 오는 경우가 있음</t>
+          <t>배송 중 해동 발생 — 배송 도중 제품이 녹아서 도착함</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3412,58 +3434,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>다채로운 종류와 맛 — 다양한 종류로 구성되어 매일 하나씩 골라 먹기 좋음</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>유용한 보냉 파우치 증정 — 도시락을 싸 들고 다닐 수 있는 보냉백이 증정되어 편함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>상품 해동 문제 — 배송 수령 시 제품이 많이 해동되어 도착함</t>
-        </is>
-      </c>
+          <t>속 편안한 포만감 — 마신 뒤 속이 더부룩하지 않고 적절한 포만감을 줌</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>우수한 휴대성 — 슬림한 팩 형태로 들고 다니며 마시기 편함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3471,51 +3493,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린 캡슐레이션 증정</t>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260914085959_597d4eafce2b4897917a1803a9f6d0ea.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1654</v>
+        <v>143</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 식후 더부룩함과 답답함이 덜하고 배변 활동에 효과적임</t>
+          <t>다양한 종류와 알찬 구성 — 골라 먹는 재미가 있고 식단 관리용으로 수량이 넉넉함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>고소한 군고구마 풍미 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>스틱형 간편 섭취 — 한 포씩 포장되어 챙겨 먹기 쉽고 휴대하기 편함</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>실용적인 보냉백 증정 — 도시락용 보냉 파우치가 증정되어 활용도가 높음</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>배송 시 해동 현상 — 수령할 때 제품이 많이 녹아 있음</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3530,7 +3552,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3540,40 +3562,36 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1533</v>
+        <v>248</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>알찬 세트 기능성 구성 — 아르기닌과 밀크씨슬 조합으로 활력과 간 건강을 동시에 챙김</t>
+          <t>6,200mg 초고함량 — 함량이 높아 운동 시 지구력 향상 및 피로 해소에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>확실한 활력 체감 — 아침에 몸이 가볍고 운동 전 섭취 시 지치지 않는 활력을 줌</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>선물용 전용 쇼핑백 증정 — 쇼핑백이 함께 구성되어 주변에 건강 선물로 전하기 깔끔함</t>
-        </is>
-      </c>
+          <t>선물용 고급 패키지 — 쇼핑백과 추가 5포 구성으로 선물 전달하기 좋음</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3589,7 +3607,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3599,38 +3617,38 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
+        <v>1533</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6,200mg 고함량 설계 — 아르기닌 함량이 매우 높아 섭취 후 피로 완화 및 체력 관리에 뛰어남</t>
+          <t>알찬 이중 케어 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있어 효율적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 액상 스틱 섭취 — 하루 1포 개별 포장으로 언제든 간편히 꺼내 마실 수 있음</t>
+          <t>확실한 피로 감소 — 복용 후 아침 일어남이 가볍고 피로감이 덜함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>고급스러운 세트 증정품 — 전용 쇼핑백과 추가 포가 증정되어 선물용으로 훌륭함</t>
+          <t>넉넉한 2개월 용량 — 용량이 넉넉하며 쇼핑백이 포함되어 구성이 훌륭함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3640,7 +3658,7 @@
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3648,50 +3666,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>운동 및 에너지는 충전 — 웨이트 등 운동 전이나 아침 공복 섭취 시 피로 회복과 에너지를 줌</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>상큼한 레몬 맛 — 레몬 맛 액상이라 약 느낌 없이 거부감 없이 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>휴대하기 편한 스틱 타입 — 액상 스틱 타입으로 물에 타 마시거나 외출 시 챙기기 용이함</t>
-        </is>
-      </c>
+          <t>탁월한 숙취 해소 — 숙취 해소 효능이 매우 뛰어남</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4020,22 +4030,22 @@
         <v>15377</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8701</v>
+        <v>8702</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>6457</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>734</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>2615</v>
@@ -4052,72 +4062,70 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 및 활력 충전 — 섭취 후 피로감이 줄고 신체에 빠른 활력이 생김
-뛰어난 체감 효과 — 몸에 잘 받고 힘이 없는 날 먹으면 효과를 체감함
-선물용으로 높은 만족도 — 받았을 때 기분이 좋고 부담 없이 선물하기 적합함</t>
+          <t>뛰어난 피로 회복 효과 — 힘이 없을 때 섭취 시 활력이 생기고 피로 해소에 큰 도움이 됨
+맛있는 맛과 간편함 — 맛이 좋고 부담 없이 간편하게 먹기 용이함
+알찬 추가 증정 구성 — 덤으로 하나 더 증정되어 선물용 및 복용 시 만족감이 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>개운한 컨디션 회복 — 면역력이 떨어지거나 바쁜 날 섭취 시 개운함과 활력을 느낌
-상큼하고 달콤한 맛 — 텁텁함 없이 상큼하고 달달한 복숭아 맛으로 부담 없이 먹음</t>
+          <t>확실한 피로 회복 및 활력 — 섭취 후 피로감이 줄어들고 다음 날 몸이 훨씬 개운해짐
+상큼달콤한 복숭아 맛 — 신맛이나 텁텁함이 적고 상큼달콤하여 가볍게 먹기 좋음
+알찬 10+1 증정 혜택 — 10개 구매 시 1개를 추가 증정하여 알차게 구성됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>지속적인 피로 해소 — 꾸준히 먹으면 지속되던 피로가 풀리고 힘이 남
-고급스러운 선물 포장 — 포장이 고급스럽게 도착하여 선물용 만족도가 높음
-부담 없는 뛰어난 맛 — 맛있게 먹을 수 있는 비타민으로 복용 부담이 없음</t>
+          <t>지속된 피로 해소 — 복용 시 피로가 잘 풀리고 몸에 에너지가 생김
+맛있는 맛과 고급 포장 — 맛이 좋고 포장이 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 비타민 — 여러 영양제를 따로 챙길 필요 없이 한 번에 섭취 가능함
-알찬 추가 증정 구성 — 단독 구성으로 추가 2입이 더 들어있어 알차게 느껴짐
-기력 회복 보조 효과 — 피로감이 덜하고 힘들 때 체력을 회복하는 느낌을 받음</t>
+          <t>빠른 컨디션 회복 — 독감 회복기나 피로할 때 생기 회복에 도움이 됨
+간편한 올인원 섭취 — 여러 영양제를 챙길 필요 없이 한 번에 간편 섭취 가능함
+단독 구성 추가 증정 — 7입에 2입을 추가 증정하여 구성이 알참</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>섭취가 편한 구미 제형 — 알약 거부감 없이 과일 향 젤리처럼 즐겁게 챙겨 먹음
-꼼꼼한 포장과 배송 — 배송이 빠르고 포장 상태가 매우 꼼꼼함</t>
+          <t>맛있고 쫀득한 구미 제형 — 새콤달콤한 과일 향 젤리 제형으로 거부감 없이 즐겨 먹음
+간편한 일상 영양 보충 — 알약 형태가 아니라 물 없이 간식처럼 쉽게 챙겨 먹음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 — 피곤한 일상에서 하나만 챙겨 먹어도 컨디션이 회복됨
-예쁜 선물 포장 패키지 — 선물용 포장이 이쁘게 되어 있어 주고받기에 감동적임
-간편한 섭취 방식 — 멀티비타민 형태라 귀찮지 않고 마시기 편함</t>
+          <t>목넘김이 쉬운 알약 크기 — 알약 크기가 크지 않아 목넘김이 용이함
+빠른 컨디션 회복 — 피로가 누적되었을 때 먹으면 컨디션 회복에 효과적임
+선물용으로 우수한 패키지 — 예쁘게 선물 포장되어 있어 부담 없이 전달하기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효능 — 피곤하고 컨디션이 안 좋을 때 회복 효과를 크게 체감함
-우수한 휴대성 및 편의성 — 가지고 다니기 편하고 마시기 간편함</t>
+          <t>확실한 컨디션 회복 — 피로감이 심할 때 복용하면 빠른 회복에 도움 됨
+우수한 휴대성 및 편의성 — 마시기 편하고 가지고 다니기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 원스톱 섭취 — 눌러서 분말과 액상을 섞어 바로 마시는 형태라 편리함
-부담 없는 깔끔한 맛 — 홍삼 성분임에도 쓴맛이 부담스럽지 않고 깔끔함
-깔끔한 패키지와 혜택 — 포장이 깔끔하며 1입 추가 증정 구성이 알참</t>
+          <t>부담 없는 복용감 — 홍삼 특유의 쓴맛이 적고 액상과 분말을 한 번에 먹기 편함
+높은 브랜드 신뢰도 — 정관장 브랜드로 믿음이 가며 추가 증정 구성도 알참</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>피로감 완화 및 개운함 — 힘들 때 마시면 다음 날 피로감이 덜하고 개운함
-고급스러운 패키지 디자인 — 포장이 고급스러워 선물용으로 받는 만족도가 높음
-맛있는 액상 비타민 — 일반 알약과 다르고 맛이 있어 섭취하기 좋음</t>
+          <t>개운한 피로 개선 — 마신 후 피로감이 덜하고 개운함이 체감됨
+고급스러운 포장 디자인 — 패키지가 고급스러워 선물용으로 기분 좋게 주고받음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>오래 유지되는 활력 효과 — 꾸준히 섭취 시 피로함이 덜하고 반짝이는 기분이 오래 유지됨
-깔끔한 포장 및 휴대성 — 포장이 깔끔하여 선물 느낌이 나고 들고 다니며 먹기 편함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>지속되는 피로 완화 — 꾸준히 먹으면 피로가 덜하고 활력이 오래 유지됨
+뛰어난 휴대성과 깔끔함 — 하루 하나씩 챙겨 다니기 편하고 포장이 깔끔함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4126,28 +4134,23 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 관련 미수령 문제 — 배송 기사 연락 문제 등으로 상품을 받지 못하는 불편 발생</t>
+          <t>상품 배송 미수령 문제 — 구매 결정은 되었으나 실제 상품을 수령하지 못함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감의 불명확함 — 맛있게 먹을 수 있으나 효능에 대한 직접적 체감은 부족함
-미세한 씁쓸한 뒷맛 — 달지 않고 약간의 씁쓸한 맛이 느껴지기도 함</t>
+          <t>약간의 씁쓸한 맛 감돎 — 달콤함 외에 미세하게 씁쓸한 잔맛이 남음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>높은 가격 부담 — 제품 성능은 좋으나 가격대가 비싼 편임</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>목넘김이 힘든 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
+          <t>다소 큰 알약 크기 — 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
     </row>
@@ -4352,47 +4355,47 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4409,34 +4412,34 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
@@ -4449,7 +4452,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>알디콤</t>
         </is>
       </c>
     </row>
@@ -4466,47 +4469,47 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린 캡슐레이션 증정</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린 캡슐레이션 증정</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
     </row>
@@ -4557,31 +4560,31 @@
         <v>30</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>732</v>
+        <v>1654</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>733</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>859</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1654</v>
-      </c>
       <c r="J19" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>1533</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>248</v>
-      </c>
       <c r="L19" s="3" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4592,71 +4595,67 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 풍미 — 달지 않고 그냥 먹거나 물에 타 먹기 맛있는 효소임
-만족스러운 포장 및 구성 — 포장이 예쁘고 굿즈 혜택 구성이 마음에 듦</t>
+          <t>맛있는 맛과 쉬운 섭취 — 달지 않고 맛있어 포 채 먹거나 물에 타기 편함
+푸짐한 구성 및 사은품 — 포토카드 등 사은품 혜택이 좋아 만족도가 높음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 핑크 포장 — 핑크빛 고급스러운 포장으로 선물받을 때 기분이 좋아짐
-피부 개선 느낌 — 꾸준히 먹으면 피부가 맑아지는 듯한 체감을 줌</t>
+          <t>식후 더부룩함 완화 — 식사 후 섭취 시 속이 편안해지고 소화와 배변에 도움 됨
+고소한 군고구마 맛 — 군고구마 맛으로 고소해서 매일 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비와 추가 증정 — 저렴한 가격에 보너스 포 및 씬칩 사은품이 추가됨
-부담 없는 맛과 포장 — 맛이 고소하여 먹기 편하고 포장이 고급스러움</t>
+          <t>예쁘고 고급스러운 포장 — 패키지와 디자인이 매우 예뻐 선물받을 때 만족감이 높음
+피부 상태 개선 느낌 — 꾸준히 복용 시 피부가 맑아지고 탱탱해지는 기분이 듦</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔한 맛 — 단백질 특유의 비리고 텁텁한 맛 없이 달콤하고 담백함
-편안한 속과 적당한 포만감 — 마신 후 더부룩하지 않고 식사 사이 허기를 달래기 좋음
-슬림한 휴대용 패키지 — 슬림하여 가방에 넣고 다니며 운동 후 간편하게 마심</t>
+          <t>합리적인 가격과 증정 — 특가 판매 및 추가 증정 혜택으로 저렴하게 구매함
+무난한 맛과 쉬운 복용 — 맛이 나쁘지 않고 복용 분량이 적당함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 많은 수량을 매우 저렴한 가격으로 가성비 있게 구매함
-물리지 않는 다양한 맛 — 뻑뻑함이 적고 맛이 다양하여 매일 먹어도 질리지 않음</t>
+          <t>부드러운 식감과 다양한 맛 — 뻑뻑함이 덜하고 부드러우며 맛이 다양해 질리지 않음
+높은 가성비 및 간편 조리 — 가격 대비 양이 많고 전자레인지로 간편 조리가 가능함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 종류와 맛 — 다양한 종류로 구성되어 매일 하나씩 골라 먹기 좋음
-유용한 보냉 파우치 증정 — 도시락을 싸 들고 다닐 수 있는 보냉백이 증정되어 편함</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리고 텁텁한 맛이 없음
+속 편안한 포만감 — 마신 뒤 속이 더부룩하지 않고 적절한 포만감을 줌
+우수한 휴대성 — 슬림한 팩 형태로 들고 다니며 마시기 편함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 식후 더부룩함과 답답함이 덜하고 배변 활동에 효과적임
-고소한 군고구마 풍미 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음
-스틱형 간편 섭취 — 한 포씩 포장되어 챙겨 먹기 쉽고 휴대하기 편함</t>
+          <t>다양한 종류와 알찬 구성 — 골라 먹는 재미가 있고 식단 관리용으로 수량이 넉넉함
+실용적인 보냉백 증정 — 도시락용 보냉 파우치가 증정되어 활용도가 높음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>알찬 세트 기능성 구성 — 아르기닌과 밀크씨슬 조합으로 활력과 간 건강을 동시에 챙김
-확실한 활력 체감 — 아침에 몸이 가볍고 운동 전 섭취 시 지치지 않는 활력을 줌
-선물용 전용 쇼핑백 증정 — 쇼핑백이 함께 구성되어 주변에 건강 선물로 전하기 깔끔함</t>
+          <t>6,200mg 초고함량 — 함량이 높아 운동 시 지구력 향상 및 피로 해소에 도움 됨
+선물용 고급 패키지 — 쇼핑백과 추가 5포 구성으로 선물 전달하기 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>6,200mg 고함량 설계 — 아르기닌 함량이 매우 높아 섭취 후 피로 완화 및 체력 관리에 뛰어남
-간편한 액상 스틱 섭취 — 하루 1포 개별 포장으로 언제든 간편히 꺼내 마실 수 있음
-고급스러운 세트 증정품 — 전용 쇼핑백과 추가 포가 증정되어 선물용으로 훌륭함</t>
+          <t>알찬 이중 케어 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있어 효율적임
+확실한 피로 감소 — 복용 후 아침 일어남이 가볍고 피로감이 덜함
+넉넉한 2개월 용량 — 용량이 넉넉하며 쇼핑백이 포함되어 구성이 훌륭함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>운동 및 에너지는 충전 — 웨이트 등 운동 전이나 아침 공복 섭취 시 피로 회복과 에너지를 줌
-상큼한 레몬 맛 — 레몬 맛 액상이라 약 느낌 없이 거부감 없이 먹기 편함
-휴대하기 편한 스틱 타입 — 액상 스틱 타입으로 물에 타 마시거나 외출 시 챙기기 용이함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>탁월한 숙취 해소 — 숙취 해소 효능이 매우 뛰어남</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4664,32 +4663,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>탄산수 혼합 시 거품 넘침 — 탄산수에 부어 섞을 경우 거품이 일어나 넘칠 수 있음</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>초기 효과 체감 미흡 — 섭취한 지 며칠 되지 않았을 때는 효과를 바로 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>복용 초기 장 반응 발생 — 복용 직후 뱃속이 꾸르륵거리거나 가스가 차는 현상이 있음
-배송 미수령 발생 — 일부 배송 누락으로 제품을 받지 못하는 경우 발생</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>탄산수 혼합 시 거품 — 탄산수에 부으면 거품이 일어나 넘칠 수 있음</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>선물 미배송 문제 — 선물이 정상적으로 배송되지 않음</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 녹아서 도착 — 배송 포장 보온 상태에 따라 제품이 녹아 오는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>상품 해동 문제 — 배송 수령 시 제품이 많이 해동되어 도착함</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
+          <t>배송 중 해동 발생 — 배송 도중 제품이 녹아서 도착함</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>배송 시 해동 현상 — 수령할 때 제품이 많이 녹아 있음</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
@@ -4707,47 +4701,47 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>19,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>25,900원</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>43,900원</t>
-        </is>
-      </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4931,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4945,51 +4939,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911058&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260710/ttaHg18AMnzwMvyaF63v610911058_00_00ttaHg18AMnzwMvyaF63v.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>6157</v>
+        <v>138</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 사 먹기 좋음</t>
+          <t>기미 개선 효능 체감 — 지속 복용 시 기미가 옅어지는 효능을 경험함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>편리한 휴대성 — 캡슐을 갖고 다니며 먹기 편하게 구성됨</t>
+          <t>꾸준한 복용 만족도 — 효과에 만족하여 반복적으로 재구매함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>낮은 성분 함량 — 가격은 저렴하나 주요 성분 함량이 다소 낮게 설정되어 있음</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -5004,12 +4994,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5019,34 +5009,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1201</v>
+        <v>1935</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>물에 타 먹는 맛있는 이온음료 — 적당한 이온음료 맛으로 물에 쉽게 타서 마시기 좋음</t>
+          <t>새콤달콤 맛있는 가루 타입 — 레모나와 유사하게 새콤하여 가루째 쉽게 먹음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가성비가 좋아 수분 보충용으로 주기적으로 구매하기 적합함</t>
+          <t>인터넷보다 저렴한 가격 — 온라인 가격보다 저렴하여 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>미미한 기능성 체감 — 수분 섭취 외에 실질적인 건강 개선 효과는 체감하기 어려움</t>
+          <t>공복 복용 시 설사 유발 — 공복에 먹으면 설사를 유발할 수 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5055,7 +5045,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5063,12 +5053,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5078,43 +5068,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 석류 맛으로 맛있고 무난하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>빠른 피로 회복 체감 — 적은 시간 자도 피로가 직빵으로 풀림</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>저렴한 구매 가격 — 부담 없는 저렴한 가격대로 이용 가능함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>적은 내용량 — 7포 구성으로 수량이 적어 아쉬움을 줌</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>액상 제형의 아쉬움 — 젤리가 아닌 액상 타입 형태로 구성되어 기대와 다를 수 있음</t>
-        </is>
-      </c>
+          <t>용량 대비 아쉬운 가성비 — 4병 구성이라 용량 대비 가격대가 아쉬움</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5122,54 +5112,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>844</v>
+        <v>710</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>과식 후 붓기 완화 보조 — 짠 음식이나 과식 후 섭취 시 다음 날 아침 붓기가 덜함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>운동 전 활력 충전 — 운동 전에 복용 시 에너지가 생김</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>만족스러운 피로 해소 — 피곤할 때 먹으면 기운이 나는 효과가 있음</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>효과 체감 미흡 — 여러 통 섭취해도 직접적인 변화나 효능을 잘 느끼지 못함</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5177,7 +5167,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5187,37 +5177,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2845</v>
+        <v>6168</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>착한 가격과 고함량 — 4000IU 고함량을 착한 가격으로 구매할 수 있어 경제적임</t>
+          <t>부담 없는 가격 — 필수 영양소를 저렴한 가격에 보충 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>하루 한 알 간편 섭취 — 알약 크기가 적당하여 하루 한 알씩 편하게 복용함</t>
+          <t>간편한 섭취 방식 — 먹기 편리하게 포장되어 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 가격은 저렴하나 핵심 성분 함량이 다소 낮음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5232,12 +5226,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5247,36 +5241,36 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1933</v>
+        <v>204</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 풍미 — 신맛이 과하지 않은 레모나 맛으로 새콤달콤해서 맛있음</t>
+          <t>간편한 필름형 제형 — 알약 형태가 아닌 필름 제형이라 섭취가 쉬움</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>가루째 편하게 먹는 제형 — 물 없이 가루째 그대로 복용해도 맛있고 편함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>온라인 대비 저렴한 가격 — 인터넷 구매보다 저렴하여 가성비 좋게 챙겨 먹음</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>착한 구매 가격 — 글루타치온 제품을 부담 없이 저렴하게 구매함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>강한 신맛 감돎 — 신맛이 다소 강해서 호불호가 갈림</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5291,58 +5285,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3648</v>
+        <v>4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>피로감 개선 효과 — 꾸준히 먹었을 때 피로를 덜 느끼게 됨</t>
+          <t>맛있는 캔디 형태 — 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>저렴한 가격과 편리성 — 가격이 저렴하고 하루 하나씩 복용하기 편함</t>
+          <t>저렴한 구매 비용 — 가격 부담 없이 구매하기 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>초기 효과 불명확 — 복용 초반에는 효과 여부를 즉각 알기 어려움</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5350,7 +5340,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5360,44 +5350,48 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3321</v>
+        <v>4575</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>대기업 제조의 높은 함량 — 대웅제약 제품으로 성분 함량이 높아 안심하고 섭취함</t>
+          <t>식후 졸음 현능 완화 — 복용 후 혈당 스파이크로 인한 졸음이 줄어듬</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>높은 구매 접근성 및 가성비 — 집 근처 다이소에서 저렴한 가격으로 손쉽게 구매 가능함</t>
+          <t>믿을 수 있는 대웅제약 — 약사 추천 및 제약사 브랜드라 안심하고 먹음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>초기 효과 체감 부족 — 초기 복용 시에는 명확한 효과 체감이 다소 미흡함</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5405,12 +5399,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5420,47 +5414,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1578</v>
+        <v>3322</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>소량 저렴 구매 가능 — 필요한 만큼 저렴하게 살 수 있어 다이소 구매 시 유용함</t>
+          <t>뛰어난 가성비와 높은 함량 — 가격 대비 높은 함량과 검증된 품질을 제공함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>익숙한 맛과 깔끔 포장 — 레몬/포도 풍미로 포장이 깔끔하여 챙겨 먹기 좋음</t>
+          <t>손쉬운 다이소 접근성 — 가까운 다이소에서 편리하게 구매 가능함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>애매한 단맛의 호불호 — 맛이 어중간하게 달아서 맛에 대한 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>효능 체감 부족 — 사람에 따라 딱히 유산균 효과를 느끼지 못할 수 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5468,12 +5454,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5483,36 +5469,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>957</v>
+        <v>6321</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있는 가르시니아 — 거부감 없이 맛있게 먹으면서 관리할 수 있음</t>
+          <t>검증된 품질 및 재구매 — 의사 추천 제품으로 복용 만족도가 높아 수차례 재구매함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 부담 없는 저렴한 가격으로 꾸준히 챙겨 먹기 적합함</t>
+          <t>합리적인 가격 및 편의성 — 가성비가 우수하고 복용하기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>불명확한 체중 감량 효과 — 정확한 컷팅 효능을 체감하기는 다소 어려움</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5627,52 +5609,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>비타민D</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
     </row>
@@ -5684,52 +5666,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -5741,52 +5723,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[의약외품][신혜선 PICK] 동국제약 멜라케어 더블 화이트 정 10정 10일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 락토핏 골드</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
     </row>
@@ -5797,25 +5779,25 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
@@ -5824,7 +5806,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5834,37 +5816,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6157</v>
+        <v>138</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1201</v>
+        <v>1935</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>844</v>
+        <v>710</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2845</v>
+        <v>6168</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1933</v>
+        <v>204</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3648</v>
+        <v>4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3321</v>
+        <v>4575</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1578</v>
+        <v>3322</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>6321</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5872,110 +5854,101 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 사 먹기 좋음
-편리한 휴대성 — 캡슐을 갖고 다니며 먹기 편하게 구성됨</t>
+          <t>기미 개선 효능 체감 — 지속 복용 시 기미가 옅어지는 효능을 경험함
+꾸준한 복용 만족도 — 효과에 만족하여 반복적으로 재구매함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>물에 타 먹는 맛있는 이온음료 — 적당한 이온음료 맛으로 물에 쉽게 타서 마시기 좋음
-부담 없는 저렴한 가격 — 가성비가 좋아 수분 보충용으로 주기적으로 구매하기 적합함</t>
+          <t>새콤달콤 맛있는 가루 타입 — 레모나와 유사하게 새콤하여 가루째 쉽게 먹음
+인터넷보다 저렴한 가격 — 온라인 가격보다 저렴하여 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 석류 맛으로 맛있고 무난하게 먹을 수 있음</t>
+          <t>빠른 피로 회복 체감 — 적은 시간 자도 피로가 직빵으로 풀림
+저렴한 구매 가격 — 부담 없는 저렴한 가격대로 이용 가능함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>과식 후 붓기 완화 보조 — 짠 음식이나 과식 후 섭취 시 다음 날 아침 붓기가 덜함</t>
+          <t>운동 전 활력 충전 — 운동 전에 복용 시 에너지가 생김
+만족스러운 피로 해소 — 피곤할 때 먹으면 기운이 나는 효과가 있음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격과 고함량 — 4000IU 고함량을 착한 가격으로 구매할 수 있어 경제적임
-하루 한 알 간편 섭취 — 알약 크기가 적당하여 하루 한 알씩 편하게 복용함</t>
+          <t>부담 없는 가격 — 필수 영양소를 저렴한 가격에 보충 가능함
+간편한 섭취 방식 — 먹기 편리하게 포장되어 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 풍미 — 신맛이 과하지 않은 레모나 맛으로 새콤달콤해서 맛있음
-가루째 편하게 먹는 제형 — 물 없이 가루째 그대로 복용해도 맛있고 편함
-온라인 대비 저렴한 가격 — 인터넷 구매보다 저렴하여 가성비 좋게 챙겨 먹음</t>
+          <t>간편한 필름형 제형 — 알약 형태가 아닌 필름 제형이라 섭취가 쉬움
+착한 구매 가격 — 글루타치온 제품을 부담 없이 저렴하게 구매함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>피로감 개선 효과 — 꾸준히 먹었을 때 피로를 덜 느끼게 됨
-저렴한 가격과 편리성 — 가격이 저렴하고 하루 하나씩 복용하기 편함</t>
+          <t>맛있는 캔디 형태 — 거부감 없이 맛있게 먹을 수 있음
+저렴한 구매 비용 — 가격 부담 없이 구매하기 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>대기업 제조의 높은 함량 — 대웅제약 제품으로 성분 함량이 높아 안심하고 섭취함
-높은 구매 접근성 및 가성비 — 집 근처 다이소에서 저렴한 가격으로 손쉽게 구매 가능함</t>
+          <t>식후 졸음 현능 완화 — 복용 후 혈당 스파이크로 인한 졸음이 줄어듬
+믿을 수 있는 대웅제약 — 약사 추천 및 제약사 브랜드라 안심하고 먹음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>소량 저렴 구매 가능 — 필요한 만큼 저렴하게 살 수 있어 다이소 구매 시 유용함
-익숙한 맛과 깔끔 포장 — 레몬/포도 풍미로 포장이 깔끔하여 챙겨 먹기 좋음</t>
+          <t>뛰어난 가성비와 높은 함량 — 가격 대비 높은 함량과 검증된 품질을 제공함
+손쉬운 다이소 접근성 — 가까운 다이소에서 편리하게 구매 가능함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 가르시니아 — 거부감 없이 맛있게 먹으면서 관리할 수 있음
-우수한 가성비 — 부담 없는 저렴한 가격으로 꾸준히 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>검증된 품질 및 재구매 — 의사 추천 제품으로 복용 만족도가 높아 수차례 재구매함
+합리적인 가격 및 편의성 — 가성비가 우수하고 복용하기 편함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>낮은 성분 함량 — 가격은 저렴하나 주요 성분 함량이 다소 낮게 설정되어 있음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>미미한 기능성 체감 — 수분 섭취 외에 실질적인 건강 개선 효과는 체감하기 어려움</t>
+          <t>공복 복용 시 설사 유발 — 공복에 먹으면 설사를 유발할 수 있음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>적은 내용량 — 7포 구성으로 수량이 적어 아쉬움을 줌
-액상 제형의 아쉬움 — 젤리가 아닌 액상 타입 형태로 구성되어 기대와 다를 수 있음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감 미흡 — 여러 통 섭취해도 직접적인 변화나 효능을 잘 느끼지 못함</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>초기 효과 불명확 — 복용 초반에는 효과 여부를 즉각 알기 어려움</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>애매한 단맛의 호불호 — 맛이 어중간하게 달아서 맛에 대한 아쉬움이 있음
-효능 체감 부족 — 사람에 따라 딱히 유산균 효과를 느끼지 못할 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>불명확한 체중 감량 효과 — 정확한 컷팅 효능을 체감하기는 다소 어려움</t>
-        </is>
-      </c>
+          <t>용량 대비 아쉬운 가성비 — 4병 구성이라 용량 대비 가격대가 아쉬움</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>상대적으로 낮은 함량 — 가격은 저렴하나 핵심 성분 함량이 다소 낮음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛 감돎 — 신맛이 다소 강해서 호불호가 갈림</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>초기 효과 체감 부족 — 초기 복용 시에는 명확한 효과 체감이 다소 미흡함</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5985,42 +5958,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6217,37 +6190,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18,400원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788483ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>5394</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>4714</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>물 없이 먹는 맛있는 구미 — 상큼하고 쫀득한 맛으로 물 없이 간식처럼 먹음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>합리적인 세일 가격 — 할인 기간을 이용해 부담 없는 가격에 쟁여두기 좋음</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -6264,41 +6245,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
+          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>18,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788483ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>695</v>
+        <v>5399</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>탄수화물 컷팅 및 체내 케어 — 탄수화물 컷팅과 글루타치온의 안색 개선을 동시에 챙김</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>빠르고 깊은 숙면 유도 — 섭취 후 뒤척임 없이 수월하게 숙면에 들어감</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100% 식물성 성분 안심 — 제약사에서 개발한 100% 식물성 성분이라 안심됨</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -6307,7 +6292,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6315,51 +6300,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>24255</v>
+        <v>41065</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 증진 효과가 큼</t>
+          <t>확실한 에너지는 충전 — 피로감이 심할 때 복용하면 활력이 크게 살아남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1일 1캡슐의 간편함 — 하루 한 알 섭취로 간편하게 두 달 동안 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>기획 구성의 혜택 — 1+1 더블기획 구성으로 세일 기간 쟁여두기 좋음</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>장기 복용 시 효능 체감 — 꾸준히 복용할수록 몸의 변화와 체력 향상이 뚜렷함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다소 비싼 가격대 — 품질은 우수하나 가격대가 높게 형성됨</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -6374,43 +6359,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>17938</v>
+        <v>14972</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>커피 한 잔 가격의 가성비 — 매우 저렴한 가격대로 다양한 영양제를 부담 없이 구매 가능함</t>
+          <t>빠른 숙면 효과 — 자기 전 복용 시 깊은 잠에 금방 빠져듦</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 섭취 및 휴대성 — 개별 포장이 되어 있어 휴대가 용이하고 챙겨 먹기 편함</t>
+          <t>맛있는 젤리 형태 — 맛있는 젤리 제형이라 섭취에 부담이 없음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6429,7 +6414,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6439,33 +6424,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>8125</v>
+        <v>24262</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>여성 질 건강 기초 케어 — 아침 공복에 챙기며 질 건강과 이너뷰티를 유지하기 적합함</t>
+          <t>확실한 장 건강 개선 — 꾸준 복용 시 장 건강과 면역력 증진에 효과적임</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>꾸준한 섭취 편의성 — 매일 아침 루틴으로 간편하게 한 알씩 챙겨 먹기 좋음</t>
+          <t>1일 1캡슐 간편함 — 하루 한 알 섭취로 장 관리가 편리함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -6476,7 +6461,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6484,37 +6469,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12,500원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014346ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>12450</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>8126</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>여성 맞춤 질유산균 — 여성 건강에 필요한 질유산균을 편리하게 보충함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>쉬운 공복 루틴 형성 — 아침 공복에 정수기 옆에서 챙겨 먹기 적합함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6523,7 +6516,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6531,58 +6524,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>닥터린 이노시톨 40:1 30포 (30일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터린</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>17,500원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206982&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020698209ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>41059</v>
+        <v>238</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 활력 충전 효과 — 피로하고 지친 컨디션에 빠른 에너지와 활력을 불어넣어 줌</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>올인원 종합 영양 케어 — 하루 한 병으로 필수 비타민과 미네랄을 한 번에 챙김</t>
-        </is>
-      </c>
+          <t>간편한 이노시톨 섭취 — 하루 한 포로 간편하게 이노시톨을 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>높은 가격대 — 체감 효과는 좋으나 타 영양제 대비 가격이 비쌈</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6590,39 +6575,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>470</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>맛있는 간식형 젤리 — 상큼하고 쫀득하여 물 없이 간식처럼 맛있게 섭취 가능함</t>
+          <t>체지방 및 장 동시 케어 — 체지방 감소와 장 건강을 동시에 관리할 수 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>합리적인 세일 가격 — 할인가로 구매 시 부담 없는 가격에 쟁여두기 좋음</t>
+          <t>상큼한 요거트 맛 — 맛있는 요거트 맛이라 하루 한 포씩 거부감 없이 챙김</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6641,58 +6630,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>14963</v>
+        <v>17954</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 수면 질 개선 — 자기 전 섭취 시 뒤척이지 않고 빠르게 푹 잘 수 있게 도움</t>
+          <t>압도적인 초저가 가성비 — 커피 한 잔 수준의 가격으로 저렴하게 복용 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>부담 없는 젤리 형태 — 식물성 성분에 구미 형태라 맛과 섭취에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>양치 후 섭취의 번거로움 — 젤리 제형 특성상 자기 전 섭취 후 다시 양치해야 함</t>
-        </is>
-      </c>
+          <t>1일 1알 개별 포장 — 개별 포장으로 위생적이며 하루 한 알로 관리가 용이함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>대기업 제조 신뢰도 — 대기업 제조 제품으로 안심하고 구매함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6700,50 +6689,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[NEW]올더베러 웰니스 스프레이 30일분 3종 택1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>9,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000265729&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026572907ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>470</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>체지방 및 장 건강 이중 케어 — 장케어와 더불어 체지방 및 아랫배 관리를 한 번에 도와줌</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>상큼한 요거트 맛 — 맛이 상큼한 요거트 맛이라 매일 하루 한 포씩 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>편안해지는 속 관리 — 복용 후 배가 더부룩한 느낌이 줄어들고 속이 편안해짐</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6869,42 +6846,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6916,52 +6893,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>대원제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>닥터린</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>씨제이웰케어</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>올더베러</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
         </is>
       </c>
     </row>
@@ -6973,52 +6950,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>닥터린 이노시톨 40:1 30포 (30일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[NEW]올더베러 웰니스 스프레이 30일분 3종 택1</t>
         </is>
       </c>
     </row>
@@ -7029,10 +7006,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4.6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.9</v>
@@ -7044,17 +7021,19 @@
         <v>4.9</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7064,32 +7043,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5394</v>
+        <v>4714</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>695</v>
+        <v>5399</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>24255</v>
+        <v>41065</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17938</v>
+        <v>14972</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8125</v>
+        <v>24262</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12450</v>
+        <v>8126</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>41059</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+        <v>238</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>470</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>14963</v>
+        <v>17954</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7098,57 +7079,61 @@
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>물 없이 먹는 맛있는 구미 — 상큼하고 쫀득한 맛으로 물 없이 간식처럼 먹음
+합리적인 세일 가격 — 할인 기간을 이용해 부담 없는 가격에 쟁여두기 좋음</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>탄수화물 컷팅 및 체내 케어 — 탄수화물 컷팅과 글루타치온의 안색 개선을 동시에 챙김</t>
+          <t>빠르고 깊은 숙면 유도 — 섭취 후 뒤척임 없이 수월하게 숙면에 들어감
+100% 식물성 성분 안심 — 제약사에서 개발한 100% 식물성 성분이라 안심됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 장 건강 및 면역 관리 — 아침 공복 복용 시 장 건강과 면역력 증진 효과가 큼
-1일 1캡슐의 간편함 — 하루 한 알 섭취로 간편하게 두 달 동안 챙겨 먹기 적합함
-기획 구성의 혜택 — 1+1 더블기획 구성으로 세일 기간 쟁여두기 좋음</t>
+          <t>확실한 에너지는 충전 — 피로감이 심할 때 복용하면 활력이 크게 살아남
+장기 복용 시 효능 체감 — 꾸준히 복용할수록 몸의 변화와 체력 향상이 뚜렷함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>커피 한 잔 가격의 가성비 — 매우 저렴한 가격대로 다양한 영양제를 부담 없이 구매 가능함
-간편한 섭취 및 휴대성 — 개별 포장이 되어 있어 휴대가 용이하고 챙겨 먹기 편함</t>
+          <t>빠른 숙면 효과 — 자기 전 복용 시 깊은 잠에 금방 빠져듦
+맛있는 젤리 형태 — 맛있는 젤리 제형이라 섭취에 부담이 없음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>여성 질 건강 기초 케어 — 아침 공복에 챙기며 질 건강과 이너뷰티를 유지하기 적합함
-꾸준한 섭취 편의성 — 매일 아침 루틴으로 간편하게 한 알씩 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+          <t>확실한 장 건강 개선 — 꾸준 복용 시 장 건강과 면역력 증진에 효과적임
+1일 1캡슐 간편함 — 하루 한 알 섭취로 장 관리가 편리함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>여성 맞춤 질유산균 — 여성 건강에 필요한 질유산균을 편리하게 보충함
+쉬운 공복 루틴 형성 — 아침 공복에 정수기 옆에서 챙겨 먹기 적합함</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 활력 충전 효과 — 피로하고 지친 컨디션에 빠른 에너지와 활력을 불어넣어 줌
-올인원 종합 영양 케어 — 하루 한 병으로 필수 비타민과 미네랄을 한 번에 챙김</t>
+          <t>간편한 이노시톨 섭취 — 하루 한 포로 간편하게 이노시톨을 챙길 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 간식형 젤리 — 상큼하고 쫀득하여 물 없이 간식처럼 맛있게 섭취 가능함
-합리적인 세일 가격 — 할인가로 구매 시 부담 없는 가격에 쟁여두기 좋음</t>
+          <t>체지방 및 장 동시 케어 — 체지방 감소와 장 건강을 동시에 관리할 수 있음
+상큼한 요거트 맛 — 맛있는 요거트 맛이라 하루 한 포씩 거부감 없이 챙김</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 수면 질 개선 — 자기 전 섭취 시 뒤척이지 않고 빠르게 푹 잘 수 있게 도움
-부담 없는 젤리 형태 — 식물성 성분에 구미 형태라 맛과 섭취에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>체지방 및 장 건강 이중 케어 — 장케어와 더불어 체지방 및 아랫배 관리를 한 번에 도와줌
-상큼한 요거트 맛 — 맛이 상큼한 요거트 맛이라 매일 하루 한 포씩 먹기 좋음
-편안해지는 속 관리 — 복용 후 배가 더부룩한 느낌이 줄어들고 속이 편안해짐</t>
-        </is>
-      </c>
+          <t>압도적인 초저가 가성비 — 커피 한 잔 수준의 가격으로 저렴하게 복용 가능함
+1일 1알 개별 포장 — 개별 포장으로 위생적이며 하루 한 알로 관리가 용이함
+대기업 제조 신뢰도 — 대기업 제조 제품으로 안심하고 구매함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7158,21 +7143,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다소 비싼 가격대 — 품질은 우수하나 가격대가 높게 형성됨</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>높은 가격대 — 체감 효과는 좋으나 타 영양제 대비 가격이 비쌈</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>양치 후 섭취의 번거로움 — 젤리 제형 특성상 자기 전 섭취 후 다시 양치해야 함</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7183,52 +7164,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>18,400원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,500원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>12,500원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>53,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>15,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>9,400원</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7358,19 +7339,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -7402,25 +7383,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7433,51 +7414,51 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7486,7 +7467,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7496,10 +7477,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7508,7 +7489,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7518,12 +7499,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
